--- a/out/Attention-Mamba1_repeat_1_000006.xlsx
+++ b/out/Attention-Mamba1_repeat_1_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.4867320633075706</v>
+        <v>2.815552302146115</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.4867320633075706</v>
+        <v>2.815552302146115</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.086732063307571</v>
+        <v>-0.3291019071641194</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.086732063307571</v>
+        <v>-0.3291019071641194</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.086732063307571</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.086732063307571</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.086732063307571</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.086732063307571</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.086732063307571</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.4867320633075706</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>0.4867320633075706</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.4867320633075706</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.4867320633075706</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.4867320633075706</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.4867320633075706</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.4867320633075706</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.4867320633075706</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.4867320633075706</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.4867320633075706</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.4867320633075706</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.4867320633075706</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.4867320633075706</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.4867320633075706</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.4867320633075706</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.4867320633075706</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.4867320633075706</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.4867320633075706</v>
+        <v>3.415552302146115</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.4867320633075706</v>
+        <v>3.415552302146115</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.4867320633075706</v>
+        <v>3.415552302146115</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.4867320633075706</v>
+        <v>3.415552302146115</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.4867320633075706</v>
+        <v>-0.3291019071641194</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.4867320633075706</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.4867320633075706</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.4867320633075706</v>
+        <v>2.815552302146115</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.4867320633075706</v>
+        <v>3.415552302146115</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.4867320633075706</v>
+        <v>3.415552302146115</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.4867320633075706</v>
+        <v>3.415552302146115</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.4867320633075706</v>
+        <v>3.415552302146115</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.4867320633075706</v>
+        <v>3.415552302146115</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.4867320633075706</v>
+        <v>3.415552302146115</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.4867320633075706</v>
+        <v>3.415552302146115</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.4867320633075706</v>
+        <v>3.415552302146115</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.4867320633075706</v>
+        <v>2.815552302146115</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.000155871572634438</v>
+        <v>-0.0004231948435447412</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.2006188557915812</v>
+        <v>0.5446845184717685</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.4867320633075706</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.4016173789615934</v>
+        <v>1.090400263945407</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.04633113988530353</v>
+        <v>-0.1257901408170543</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.4867320633075706</v>
+        <v>2.815552302146115</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.1541318443336433</v>
+        <v>0.4184711828111694</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.4867320633075706</v>
+        <v>2.815552302146115</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.1541318443336433</v>
+        <v>0.4184711828111694</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.4867320633075706</v>
+        <v>3.415552302146115</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.1539690906040873</v>
+        <v>0.4179210449182205</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.5000144935651735</v>
+        <v>1.690142422818905</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.4867320633075706</v>
+        <v>3.415552302146115</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.154994048642978</v>
+        <v>3.801571684337854</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.09567220145030574</v>
+        <v>0.323389770763705</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.4867320633075706</v>
+        <v>3.415552302146115</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.845593959667725</v>
+        <v>2.755742045935011</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.167578934209011</v>
+        <v>0.5664476356239772</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.4867320633075706</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.085126524412855</v>
+        <v>3.565406505077432</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.09177232267009613</v>
+        <v>0.3102075768965671</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.4867320633075706</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.100947792628159</v>
+        <v>3.618885344162097</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.03790310895811631</v>
+        <v>0.1281202469003695</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.4867320633075706</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.084885875870534</v>
+        <v>3.564593066827695</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.04722451155623718</v>
+        <v>0.1596268330990471</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.4867320633075706</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.141437758335411</v>
+        <v>3.75574799053522</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.02843466546628309</v>
+        <v>0.09611538230890987</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.4867320633075706</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.151051713348663</v>
+        <v>3.788244781568208</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.02161888781390162</v>
+        <v>0.07307352908502128</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.4867320633075706</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.165841491340088</v>
+        <v>3.838236001925585</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.009559359650552801</v>
+        <v>0.03232061208230283</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-2.791318200473973</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.163325781724864</v>
+        <v>3.829739039944887</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.007584335346080537</v>
+        <v>0.02564790978787479</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.4867320633075706</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.168933272039792</v>
+        <v>3.848701017955487</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.003759727796274096</v>
+        <v>0.01271752861916947</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.4867320633075706</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.168861080992258</v>
+        <v>3.848468952395511</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.002182718960713415</v>
+        <v>0.007393097496135923</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.086732063307571</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.169467713688232</v>
+        <v>3.850530899027135</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.001088859480356707</v>
+        <v>0.003692594147695146</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-2.791318200473973</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.169461351759338</v>
+        <v>3.850521295272814</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0005354338545277601</v>
+        <v>0.001823276231274763</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-2.791318200473973</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.169442636625065</v>
+        <v>3.850470014296472</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0003087393611228572</v>
+        <v>0.00105637358337307</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-2.791318200473973</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.16952486076333</v>
+        <v>3.850758523483768</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>9.990259535667968e-05</v>
+        <v>0.0003498832481215334</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-2.791318200473973</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.16941456271158</v>
+        <v>3.850401047410001</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>4.889898753450504e-05</v>
+        <v>0.0001724175006344124</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.4867320633075706</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.169410159115746</v>
+        <v>3.850398024411353</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>2.435435356130208e-05</v>
+        <v>9.284784520434025e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-2.791318200473973</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.169409937823393</v>
+        <v>3.850408953436843</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>9.221082681779568e-06</v>
+        <v>4.240360893926523e-05</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.086732063307571</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.169404006691956</v>
+        <v>3.850400849665385</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>3.727602236888622e-06</v>
+        <v>2.409200745629541e-05</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>1.086732063307571</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.169402233832903</v>
+        <v>3.850406606801875</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>-2.422504053549707e-06</v>
+        <v>7.887479732251461e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>1.086732063307571</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.169396234299306</v>
+        <v>3.850398269650506</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>-2.042425637823487e-06</v>
+        <v>9.151487243530285e-07</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>1.086732063307571</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.169391991689152</v>
+        <v>3.850395164965256</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0</v>
+        <v>-1.814378588387752e-06</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-2.191318200473974</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.169392220010187</v>
+        <v>3.850390845974106</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0</v>
+        <v>-1.724541871943372e-06</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>1.086732063307571</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.169392309954837</v>
+        <v>3.850386021801218</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.4867320633075706</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.169391452021252</v>
+        <v>3.850385163867633</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>1.086732063307571</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.169391680342287</v>
+        <v>3.850385392188667</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>1.086732063307571</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.169390884678075</v>
+        <v>3.850384596524456</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-2.791318200473973</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.169390946947448</v>
+        <v>3.850384658793828</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.4867320633075706</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.169390974622725</v>
+        <v>3.850384686469105</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.4867320633075706</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.169391126836748</v>
+        <v>3.850384838683128</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-2.791318200473973</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.169390780895786</v>
+        <v>3.850384492742167</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.4867320633075706</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.169390857002798</v>
+        <v>3.850384568849178</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-2.791318200473973</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.16939102305446</v>
+        <v>3.85038473490084</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.4867320633075706</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.169391382833059</v>
+        <v>3.85038509467944</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.4867320633075706</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.169391403589517</v>
+        <v>3.850385115435897</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.086732063307571</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.169391507371806</v>
+        <v>3.850385219218186</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-2.191318200473974</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.16939173569284</v>
+        <v>3.850385447539221</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-2.791318200473973</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.169391611154094</v>
+        <v>3.850385323000475</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-2.791318200473973</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.169391638829371</v>
+        <v>3.850385350675751</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.4867320633075706</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.169391694179925</v>
+        <v>3.850385406026306</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-2.791318200473973</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.169391957095056</v>
+        <v>3.850385668941436</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-2.791318200473973</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.169391874069225</v>
+        <v>3.850385585915606</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-2.791318200473973</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.169391666504648</v>
+        <v>3.850385378351029</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-2.791318200473973</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.169391680342287</v>
+        <v>3.850385392188667</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-2.791318200473973</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.169391818718671</v>
+        <v>3.850385530565051</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-2.791318200473973</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.169391535047083</v>
+        <v>3.850385246893464</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-2.791318200473973</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.169391362076602</v>
+        <v>3.850385073922983</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.086732063307571</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.169391258294314</v>
+        <v>3.850384970140694</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-2.191318200473974</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.169391403589517</v>
+        <v>3.850385115435897</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-2.191318200473974</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.169391645748191</v>
+        <v>3.850385357594571</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-2.791318200473973</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.16939147277771</v>
+        <v>3.85038518462409</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-2.791318200473973</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.169391175268483</v>
+        <v>3.850384887114863</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-2.791318200473973</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.169391161430844</v>
+        <v>3.850384873277225</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-2.791318200473973</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.169390794733425</v>
+        <v>3.850384506579805</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.086732063307571</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.169390794733425</v>
+        <v>3.850384506579805</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>1.086732063307571</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.169390732464052</v>
+        <v>3.850384444310432</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-2.191318200473974</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.169390628681763</v>
+        <v>3.850384340528143</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>1.086732063307571</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.169390455711282</v>
+        <v>3.850384167557663</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>1.086732063307571</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.169390504143017</v>
+        <v>3.850384215989398</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>1.086732063307571</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.169390144364417</v>
+        <v>3.850383856210797</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.086732063307571</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.169390102851502</v>
+        <v>3.850383814697882</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>1.086732063307571</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.169390158202055</v>
+        <v>3.850383870048436</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-2.791318200473973</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.16939021355261</v>
+        <v>3.85038392539899</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.4867320633075706</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.169390255065525</v>
+        <v>3.850383966911906</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.4867320633075706</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.169389985231575</v>
+        <v>3.850383697077955</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.086732063307571</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.169390040582128</v>
+        <v>3.850383752428509</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-2.791318200473973</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.169390185877333</v>
+        <v>3.850383897723713</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.4867320633075706</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.169390151283236</v>
+        <v>3.850383863129617</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.4867320633075706</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.169390137445598</v>
+        <v>3.850383849291978</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.086732063307571</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.169390227390248</v>
+        <v>3.850383939236628</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>1.086732063307571</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.169390545655932</v>
+        <v>3.850384257502313</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-2.791318200473973</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.169390365766632</v>
+        <v>3.850384077613013</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.4867320633075706</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.169390407279548</v>
+        <v>3.850384119125929</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.4867320633075706</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.169390220471429</v>
+        <v>3.850383932317809</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>1.086732063307571</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.169390289659621</v>
+        <v>3.850384001506002</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>1.086732063307571</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.169390089013863</v>
+        <v>3.850383800860244</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.086732063307571</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.169390130526779</v>
+        <v>3.850383842373159</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.086732063307571</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.169390158202055</v>
+        <v>3.850383870048436</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-Mamba1_repeat_1_000006.xlsx
+++ b/out/Attention-Mamba1_repeat_1_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.4867320633075706</v>
+        <v>0.4994734148394769</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.4867320633075706</v>
+        <v>0.4994734148394769</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.086732063307571</v>
+        <v>0.699473414839477</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.086732063307571</v>
+        <v>0.699473414839477</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.086732063307571</v>
+        <v>0.699473414839477</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.086732063307571</v>
+        <v>0.699473414839477</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.086732063307571</v>
+        <v>0.699473414839477</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.086732063307571</v>
+        <v>0.699473414839477</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.086732063307571</v>
+        <v>0.699473414839477</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.4867320633075706</v>
+        <v>0.4994734148394769</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>0.4867320633075706</v>
+        <v>0.4994734148394769</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.4867320633075706</v>
+        <v>0.4994734148394769</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.4867320633075706</v>
+        <v>0.4994734148394769</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.4867320633075706</v>
+        <v>0.4994734148394769</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.4867320633075706</v>
+        <v>0.4994734148394769</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.4867320633075706</v>
+        <v>0.4994734148394769</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.4867320633075706</v>
+        <v>0.4994734148394769</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.4867320633075706</v>
+        <v>0.4994734148394769</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.4867320633075706</v>
+        <v>0.4994734148394769</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.4867320633075706</v>
+        <v>0.4994734148394769</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.4867320633075706</v>
+        <v>0.4994734148394769</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.4867320633075706</v>
+        <v>0.4994734148394769</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.4867320633075706</v>
+        <v>0.4994734148394769</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.4867320633075706</v>
+        <v>0.4994734148394769</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.4867320633075706</v>
+        <v>0.4994734148394769</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.4867320633075706</v>
+        <v>0.4994734148394769</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.4867320633075706</v>
+        <v>0.4994734148394769</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.4867320633075706</v>
+        <v>0.4994734148394769</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.4867320633075706</v>
+        <v>0.4994734148394769</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.4867320633075706</v>
+        <v>0.4994734148394769</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.4867320633075706</v>
+        <v>0.4994734148394769</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.4867320633075706</v>
+        <v>0.4994734148394769</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.4867320633075706</v>
+        <v>0.4994734148394769</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.4867320633075706</v>
+        <v>0.4994734148394769</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.4867320633075706</v>
+        <v>0.4994734148394769</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.4867320633075706</v>
+        <v>0.4994734148394769</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.4867320633075706</v>
+        <v>0.4994734148394769</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.4867320633075706</v>
+        <v>0.4994734148394769</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.4867320633075706</v>
+        <v>0.4994734148394769</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.4867320633075706</v>
+        <v>0.4994734148394769</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.4867320633075706</v>
+        <v>0.4994734148394769</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.4867320633075706</v>
+        <v>0.4994734148394769</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.4867320633075706</v>
+        <v>0.4994734148394769</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.000155871572634438</v>
+        <v>-0.0001573340899131727</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.2006188557915812</v>
+        <v>0.2025012294539711</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.4867320633075706</v>
+        <v>0.4994734148394769</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.4016173789615934</v>
+        <v>0.4053856886428169</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.04633113988530353</v>
+        <v>-0.04676585733558746</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.4867320633075706</v>
+        <v>0.4994734148394769</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.1541318443336433</v>
+        <v>0.1555780380284705</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.4867320633075706</v>
+        <v>0.4994734148394769</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.1541318443336433</v>
+        <v>0.1555780380284705</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.4867320633075706</v>
+        <v>0.4994734148394769</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.1539690906040873</v>
+        <v>0.1554138395080659</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.5000144935651735</v>
+        <v>0.5044532035165206</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.4867320633075706</v>
+        <v>0.4994734148394769</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.154994048642978</v>
+        <v>1.165325055958615</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.09567220145030574</v>
+        <v>0.096521436488908</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.4867320633075706</v>
+        <v>0.4994734148394769</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.845593959667725</v>
+        <v>0.8531783740468305</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.167578934209011</v>
+        <v>0.1690664499189515</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.4867320633075706</v>
+        <v>0.4994734148394769</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.085126524412855</v>
+        <v>1.09483746280859</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.09177232267009613</v>
+        <v>0.09258717866642957</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.4867320633075706</v>
+        <v>0.4994734148394769</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.100947792628159</v>
+        <v>1.110799209709622</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.03790310895811631</v>
+        <v>0.03823965635158405</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.4867320633075706</v>
+        <v>0.4994734148394769</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.084885875870534</v>
+        <v>1.094594677519507</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.04722451155623718</v>
+        <v>0.04764333030786268</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.4867320633075706</v>
+        <v>0.4994734148394769</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.141437758335411</v>
+        <v>1.151648688238389</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.02843466546628309</v>
+        <v>0.02868743904704928</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.4867320633075706</v>
+        <v>0.4994734148394769</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.151051713348663</v>
+        <v>1.161348105945724</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.02161888781390162</v>
+        <v>0.02181106368796389</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.4867320633075706</v>
+        <v>-0.2497952168820189</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.165841491340088</v>
+        <v>1.176269354091264</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.009559359650552801</v>
+        <v>0.009645181422093153</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-2.791318200473973</v>
+        <v>-0.2497952168820188</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.163325781724864</v>
+        <v>1.173731325102975</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.007584335346080537</v>
+        <v>0.007652435065038388</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.4867320633075706</v>
+        <v>-0.2497952168820188</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.168933272039792</v>
+        <v>1.179388234324933</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.003759727796274096</v>
+        <v>0.003792247039697061</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.4867320633075706</v>
+        <v>0.4994734148394769</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.168861080992258</v>
+        <v>1.179315462889612</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.002182718960713415</v>
+        <v>0.002203083365932822</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.086732063307571</v>
+        <v>-0.2497952168820189</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.169467713688232</v>
+        <v>1.179927376964878</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.001088859480356707</v>
+        <v>0.001097587082593596</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-2.791318200473973</v>
+        <v>-0.9990638486035147</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.169461351759338</v>
+        <v>1.17992100416953</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0005354338545277601</v>
+        <v>0.0005411831508525235</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-2.791318200473973</v>
+        <v>-1.74833248032501</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.169442636625065</v>
+        <v>1.179902178091691</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0003087393611228572</v>
+        <v>0.00031207701390076</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-2.791318200473973</v>
+        <v>-1.74833248032501</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.16952486076333</v>
+        <v>1.179984861653934</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-2.791318200473973</v>
+        <v>-0.9990638486035147</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.16941456271158</v>
+        <v>1.179874563602183</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.4867320633075706</v>
+        <v>-0.9990638486035147</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.169410159115746</v>
+        <v>1.179870160006349</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-2.791318200473973</v>
+        <v>-0.2497952168820188</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.169409937823393</v>
+        <v>1.179869938713997</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.086732063307571</v>
+        <v>-0.04979521688201877</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.169404006691956</v>
+        <v>1.179864007582559</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>1.086732063307571</v>
+        <v>0.699473414839477</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.169402233832903</v>
+        <v>1.179862234723506</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>1.086732063307571</v>
+        <v>0.699473414839477</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.169396234299306</v>
+        <v>1.179856235189909</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>1.086732063307571</v>
+        <v>-0.04979521688201882</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.169391991689152</v>
+        <v>1.179851992579755</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-2.191318200473974</v>
+        <v>-0.04979521688201885</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.169392220010187</v>
+        <v>1.17985222090079</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>1.086732063307571</v>
+        <v>-0.04979521688201885</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.169392309954837</v>
+        <v>1.17985231084544</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.4867320633075706</v>
+        <v>0.699473414839477</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.169391452021252</v>
+        <v>1.179851452911855</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>1.086732063307571</v>
+        <v>0.699473414839477</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.169391680342287</v>
+        <v>1.17985168123289</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>1.086732063307571</v>
+        <v>-0.04979521688201877</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.169390884678075</v>
+        <v>1.179850885568678</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-2.791318200473973</v>
+        <v>-0.2497952168820188</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.169390946947448</v>
+        <v>1.179850947838051</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.4867320633075706</v>
+        <v>-0.2497952168820188</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.169390974622725</v>
+        <v>1.179850975513328</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.4867320633075706</v>
+        <v>-0.2497952168820188</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.169391126836748</v>
+        <v>1.179851127727351</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-2.791318200473973</v>
+        <v>-0.2497952168820188</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.169390780895786</v>
+        <v>1.17985078178639</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.4867320633075706</v>
+        <v>-0.9990638486035147</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.169390857002798</v>
+        <v>1.179850857893401</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-2.791318200473973</v>
+        <v>-0.2497952168820188</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.16939102305446</v>
+        <v>1.179851023945063</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.4867320633075706</v>
+        <v>-0.2497952168820188</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.169391382833059</v>
+        <v>1.179851383723663</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.4867320633075706</v>
+        <v>0.699473414839477</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.169391403589517</v>
+        <v>1.179851404480121</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.086732063307571</v>
+        <v>-0.04979521688201882</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.169391507371806</v>
+        <v>1.179851508262409</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-2.191318200473974</v>
+        <v>-0.7990638486035146</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.16939173569284</v>
+        <v>1.179851736583444</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-2.791318200473973</v>
+        <v>-1.74833248032501</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.169391611154094</v>
+        <v>1.179851612044698</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-2.791318200473973</v>
+        <v>-0.9990638486035147</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.169391638829371</v>
+        <v>1.179851639719975</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.4867320633075706</v>
+        <v>-0.9990638486035147</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.169391694179925</v>
+        <v>1.179851695070528</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-2.791318200473973</v>
+        <v>-0.9990638486035147</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.169391957095056</v>
+        <v>1.179851957985659</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-2.791318200473973</v>
+        <v>-1.74833248032501</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.169391874069225</v>
+        <v>1.179851874959828</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-2.791318200473973</v>
+        <v>-1.74833248032501</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.169391666504648</v>
+        <v>1.179851667395251</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-2.791318200473973</v>
+        <v>-1.74833248032501</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.169391680342287</v>
+        <v>1.17985168123289</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-2.791318200473973</v>
+        <v>-1.74833248032501</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.169391818718671</v>
+        <v>1.179851819609275</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-2.791318200473973</v>
+        <v>-1.74833248032501</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.169391535047083</v>
+        <v>1.179851535937686</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-2.791318200473973</v>
+        <v>-0.9990638486035147</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.169391362076602</v>
+        <v>1.179851362967205</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.086732063307571</v>
+        <v>-0.7990638486035146</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.169391258294314</v>
+        <v>1.179851259184917</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-2.191318200473974</v>
+        <v>-0.7990638486035146</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.169391403589517</v>
+        <v>1.179851404480121</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-2.191318200473974</v>
+        <v>-1.54833248032501</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.169391645748191</v>
+        <v>1.179851646638794</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-2.791318200473973</v>
+        <v>-1.54833248032501</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.16939147277771</v>
+        <v>1.179851473668313</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-2.791318200473973</v>
+        <v>-1.74833248032501</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.169391175268483</v>
+        <v>1.179851176159086</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-2.791318200473973</v>
+        <v>-1.74833248032501</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.169391161430844</v>
+        <v>1.179851162321447</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-2.791318200473973</v>
+        <v>-0.9990638486035147</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.169390794733425</v>
+        <v>1.179850795624028</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.086732063307571</v>
+        <v>-0.04979521688201882</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.169390794733425</v>
+        <v>1.179850795624028</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>1.086732063307571</v>
+        <v>-0.04979521688201882</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.169390732464052</v>
+        <v>1.179850733354655</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-2.191318200473974</v>
+        <v>-0.04979521688201885</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.169390628681763</v>
+        <v>1.179850629572366</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>1.086732063307571</v>
+        <v>-0.04979521688201885</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.169390455711282</v>
+        <v>1.179850456601886</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>1.086732063307571</v>
+        <v>0.699473414839477</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.169390504143017</v>
+        <v>1.17985050503362</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>1.086732063307571</v>
+        <v>0.699473414839477</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.169390144364417</v>
+        <v>1.17985014525502</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.086732063307571</v>
+        <v>0.699473414839477</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.169390102851502</v>
+        <v>1.179850103742105</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>1.086732063307571</v>
+        <v>-0.04979521688201882</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.169390158202055</v>
+        <v>1.179850159092659</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-2.791318200473973</v>
+        <v>-0.04979521688201877</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.16939021355261</v>
+        <v>1.179850214443213</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.4867320633075706</v>
+        <v>-0.2497952168820188</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.169390255065525</v>
+        <v>1.179850255956128</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.4867320633075706</v>
+        <v>0.4994734148394769</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.169389985231575</v>
+        <v>1.179849986122178</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.086732063307571</v>
+        <v>-0.2497952168820189</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.169390040582128</v>
+        <v>1.179850041472732</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-2.791318200473973</v>
+        <v>-0.2497952168820189</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.169390185877333</v>
+        <v>1.179850186767936</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.4867320633075706</v>
+        <v>-0.2497952168820189</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.169390151283236</v>
+        <v>1.17985015217384</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.4867320633075706</v>
+        <v>0.4994734148394769</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.169390137445598</v>
+        <v>1.179850138336201</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.086732063307571</v>
+        <v>0.699473414839477</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.169390227390248</v>
+        <v>1.179850228280851</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>1.086732063307571</v>
+        <v>-0.04979521688201882</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.169390545655932</v>
+        <v>1.179850546546536</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-2.791318200473973</v>
+        <v>-0.04979521688201885</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.169390365766632</v>
+        <v>1.179850366657236</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.4867320633075706</v>
+        <v>-0.2497952168820189</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.169390407279548</v>
+        <v>1.179850408170151</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.4867320633075706</v>
+        <v>0.4994734148394769</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.169390220471429</v>
+        <v>1.179850221362032</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>1.086732063307571</v>
+        <v>0.699473414839477</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.169390289659621</v>
+        <v>1.179850290550224</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>1.086732063307571</v>
+        <v>0.699473414839477</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.169390089013863</v>
+        <v>1.179850089904467</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.086732063307571</v>
+        <v>0.699473414839477</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.169390130526779</v>
+        <v>1.179850131417382</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.086732063307571</v>
+        <v>0.699473414839477</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.169390158202055</v>
+        <v>1.179850159092659</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-Mamba1_repeat_1_000006.xlsx
+++ b/out/Attention-Mamba1_repeat_1_000006.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0.006207163445651531</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.4994734148394769</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.006342182867228985</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.4994734148394769</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.006411452777683735</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.699473414839477</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.006846233271062374</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.699473414839477</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.005792059935629368</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.699473414839477</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.006360054947435856</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.699473414839477</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.005367246456444263</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.699473414839477</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.006550620310008526</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.699473414839477</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.006490088067948818</v>
       </c>
       <c r="JB10" t="n">
-        <v>0.699473414839477</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.005696640349924564</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.4994734148394769</v>
+        <v>-0.16</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.005532250739634037</v>
       </c>
       <c r="JB12" t="n">
-        <v>0.4994734148394769</v>
+        <v>-0.3</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.00515605416148901</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.4994734148394769</v>
+        <v>-0.3</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.005981327034533024</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.4994734148394769</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.004941192455589771</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.4994734148394769</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.004974578507244587</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.4994734148394769</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.005092139355838299</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.4994734148394769</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.005633248947560787</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.4994734148394769</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.005953357554972172</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.4994734148394769</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.006602124311029911</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.4994734148394769</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.005436302162706852</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.4994734148394769</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.005349772982299328</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.4994734148394769</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.005134754814207554</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.4994734148394769</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.005302916280925274</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.4994734148394769</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.006316087208688259</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.4994734148394769</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.005086249671876431</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.4994734148394769</v>
+        <v>0.3</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.006834325380623341</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.4994734148394769</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.009803268127143383</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.4994734148394769</v>
+        <v>0.3</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.005910732783377171</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.4994734148394769</v>
+        <v>0.3</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.005230660550296307</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.4994734148394769</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.005556081421673298</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.4994734148394769</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.004580830223858356</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.4994734148394769</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.004326946102082729</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.4994734148394769</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.004814106039702892</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.4994734148394769</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.006981401704251766</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.4994734148394769</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.005062269978225231</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.4994734148394769</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.005026125349104404</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.4994734148394769</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.005594893358647823</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.4994734148394769</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.004462697543203831</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.4994734148394769</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.004877683706581593</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.4994734148394769</v>
+        <v>0.16</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.005536851473152637</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.4994734148394769</v>
+        <v>0.3</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.006697596050798893</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.4994734148394769</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.006844854913651943</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.4994734148394769</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.00935364980250597</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.4994734148394769</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0001573340899131727</v>
+        <v>-0.0001665776765915798</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.2025012294539711</v>
+        <v>0.2143982350876445</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.005945404060184956</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.4994734148394769</v>
+        <v>0.3</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.4053856886428169</v>
+        <v>0.4292026366520683</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.04676585733558746</v>
+        <v>-0.04951346215049699</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.002955780364573002</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.4994734148394769</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.1555780380284705</v>
+        <v>0.1647181952605559</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.005179510451853275</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.4994734148394769</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.1555780380284705</v>
+        <v>0.1647181952605559</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.004848345182836056</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.4994734148394769</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.1554138395080659</v>
+        <v>0.1646723944821758</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.5044532035165206</v>
+        <v>0.1407097342177126</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.003350836224853992</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.4994734148394769</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.165325055958615</v>
+        <v>0.4463723740707271</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.096521436488908</v>
+        <v>0.02692328427075105</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.006065732799470425</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.4994734148394769</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.8531783740468305</v>
+        <v>0.3593035450629278</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.1690664499189515</v>
+        <v>0.04715846821639863</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.004219301976263523</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.4994734148394769</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.09483746280859</v>
+        <v>0.4267108302913485</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.09258717866642957</v>
+        <v>0.02582569332005032</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.004448720254004002</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.4994734148394769</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.110799209709622</v>
+        <v>0.4311631424777601</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.03823965635158405</v>
+        <v>0.01066545222319475</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.003080525435507298</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.4994734148394769</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.094594677519507</v>
+        <v>0.4266421324262565</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.04764333030786268</v>
+        <v>0.01328882626882174</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.007585323415696621</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.4994734148394769</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.151648688238389</v>
+        <v>0.4425563530846408</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.02868743904704928</v>
+        <v>0.008000147476434879</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.0009712046012282372</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.4994734148394769</v>
+        <v>0.16</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.161348105945724</v>
+        <v>0.445259625527042</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.02181106368796389</v>
+        <v>0.006080109822821451</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.01057935412973166</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.2497952168820189</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.176269354091264</v>
+        <v>0.4494187597840151</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.009645181422093153</v>
+        <v>0.00268726075906222</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.001564680598676205</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.2497952168820188</v>
+        <v>0.16</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.173731325102975</v>
+        <v>0.4487070814068473</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.007652435065038388</v>
+        <v>0.002131313405825927</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.0008056936785578728</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.2497952168820188</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.179388234324933</v>
+        <v>0.4502816720231185</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.003792247039697061</v>
+        <v>0.001053126151378035</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.02222119271755219</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.4994734148394769</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.179315462889612</v>
+        <v>0.450257766341008</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.002203083365932822</v>
+        <v>0.0006117505580734626</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.008746686391532421</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.2497952168820189</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.179927376964878</v>
+        <v>0.4504250796268531</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.001097587082593596</v>
+        <v>0.0003033752790367313</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.002759278751909733</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.9990638486035147</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.17992100416953</v>
+        <v>0.4504196956788138</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0005411831508525235</v>
+        <v>0.0001473563526062303</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.002197650261223316</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.74833248032501</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.179902178091691</v>
+        <v>0.4504108389307852</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.00031207701390076</v>
+        <v>8.177897222547117e-05</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.0001791389659047127</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.74833248032501</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.179984861653934</v>
+        <v>0.4504303000981822</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>9.990259535667968e-05</v>
+        <v>2.40156114816348e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.0017900625243783</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.9990638486035147</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.179874563602183</v>
+        <v>0.4503953742886209</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>4.889898753450504e-05</v>
+        <v>1.07205380308973e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.0006416859105229378</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.9990638486035147</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.179870160006349</v>
+        <v>0.450390548239836</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>2.435435356130208e-05</v>
+        <v>2.338588390325519e-06</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.0007145730778574944</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.2497952168820188</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.179869938713997</v>
+        <v>0.4503869435625053</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>9.221082681779568e-06</v>
+        <v>-2.596391060734771e-07</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.001293000765144825</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.04979521688201877</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.179864007582559</v>
+        <v>0.4503816331853594</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>3.727602236888622e-06</v>
+        <v>-2.090799254370459e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.001239358447492123</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.699473414839477</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.179862234723506</v>
+        <v>0.4503777088990084</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>-2.422504053549707e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>9.129848331212997e-05</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.699473414839477</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.179856235189909</v>
+        <v>0.4503773767956851</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>-2.042425637823487e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.001452044583857059</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.04979521688201882</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.179851992579755</v>
+        <v>0.4503777573307429</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.001405653543770313</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.04979521688201885</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.17985222090079</v>
+        <v>0.4503779856517776</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>3.915745764970779e-05</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.04979521688201885</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.17985231084544</v>
+        <v>0.4503780755964276</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0.0001948131248354912</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.699473414839477</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.179851452911855</v>
+        <v>0.4503772176628427</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.001030710525810719</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.699473414839477</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.17985168123289</v>
+        <v>0.4503774459838774</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.0008104080334305763</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.04979521688201877</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.179850885568678</v>
+        <v>0.4503766503196657</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.000362263061106205</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.2497952168820188</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.179850947838051</v>
+        <v>0.4503767125890388</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.0002335542812943459</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.2497952168820188</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.179850975513328</v>
+        <v>0.4503767402643156</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.0006411010399460793</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.2497952168820188</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.179851127727351</v>
+        <v>0.4503768924783389</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.0004367930814623833</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.2497952168820188</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.17985078178639</v>
+        <v>0.4503765465373772</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.0002755699679255486</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.9990638486035147</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.179850857893401</v>
+        <v>0.4503766226443888</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.0006333636119961739</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.2497952168820188</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.179851023945063</v>
+        <v>0.4503767886960504</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.001151957549154758</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.2497952168820188</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.179851383723663</v>
+        <v>0.4503771484746504</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.0009500766173005104</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.699473414839477</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.179851404480121</v>
+        <v>0.4503771692311082</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.001128560863435268</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.04979521688201882</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.179851508262409</v>
+        <v>0.4503772730133966</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.001120119355618954</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.7990638486035146</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.179851736583444</v>
+        <v>0.4503775013344313</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.0005965391173958778</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.74833248032501</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.179851612044698</v>
+        <v>0.4503773767956851</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.0004362137988209724</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.9990638486035147</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.179851639719975</v>
+        <v>0.450377404470962</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.001077928580343723</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.9990638486035147</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.179851695070528</v>
+        <v>0.4503774598215159</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.001127165742218494</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.9990638486035147</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.179851957985659</v>
+        <v>0.4503777227366467</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.0001120949164032936</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.74833248032501</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.179851874959828</v>
+        <v>0.4503776397108158</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.0004843929782509804</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.74833248032501</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.179851667395251</v>
+        <v>0.4503774321462391</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.0005521578714251518</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.74833248032501</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.17985168123289</v>
+        <v>0.4503774459838774</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.0007966244593262672</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.74833248032501</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.179851819609275</v>
+        <v>0.4503775843602622</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.0006675319746136665</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.74833248032501</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.179851535937686</v>
+        <v>0.4503773006886735</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.000567135401070118</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.9990638486035147</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.179851362967205</v>
+        <v>0.4503771277181928</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.0003354726359248161</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.7990638486035146</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.179851259184917</v>
+        <v>0.4503770239359043</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.0008710445836186409</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.7990638486035146</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.179851404480121</v>
+        <v>0.4503771692311082</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.0009327111765742302</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.54833248032501</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.179851646638794</v>
+        <v>0.4503774113897814</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.0008830046281218529</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.54833248032501</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.179851473668313</v>
+        <v>0.4503772384193004</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.0005200998857617378</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.74833248032501</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.179851176159086</v>
+        <v>0.4503769409100735</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.0002966606989502907</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.74833248032501</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.179851162321447</v>
+        <v>0.4503769270724349</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.0003482317551970482</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.9990638486035147</v>
+        <v>0.16</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.179850795624028</v>
+        <v>0.4503765603750157</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.0001257872208952904</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.04979521688201882</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.179850795624028</v>
+        <v>0.4503765603750157</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.0006639258936047554</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.04979521688201882</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.179850733354655</v>
+        <v>0.4503764981056426</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.000521278940141201</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.04979521688201885</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.179850629572366</v>
+        <v>0.4503763943233541</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0.0002198508009314537</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.04979521688201885</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.179850456601886</v>
+        <v>0.4503762213528734</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>9.657349437475204e-05</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.699473414839477</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.17985050503362</v>
+        <v>0.4503762697846079</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0.0003365101292729378</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.699473414839477</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.17985014525502</v>
+        <v>0.4503759100060079</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.0003854716196656227</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.699473414839477</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.179850103742105</v>
+        <v>0.4503758684930925</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.0006475178524851799</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.04979521688201882</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.179850159092659</v>
+        <v>0.4503759238436462</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.0002286871895194054</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.04979521688201877</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.179850214443213</v>
+        <v>0.4503759791942001</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>6.584916263818741e-05</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.2497952168820188</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.179850255956128</v>
+        <v>0.4503760207071155</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.0003580143675208092</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.4994734148394769</v>
+        <v>-0.16</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.179849986122178</v>
+        <v>0.4503757508731654</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.0003768233582377434</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.2497952168820189</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.179850041472732</v>
+        <v>0.4503758062237194</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-6.425194442272186e-06</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.2497952168820189</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.179850186767936</v>
+        <v>0.4503759515189233</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.0001192344352602959</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.2497952168820189</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.17985015217384</v>
+        <v>0.450375916924827</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>6.986316293478012e-05</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.4994734148394769</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.179850138336201</v>
+        <v>0.4503759030871885</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.001394783146679401</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.699473414839477</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.179850228280851</v>
+        <v>0.4503759930318387</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.003585808910429478</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.04979521688201882</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.179850546546536</v>
+        <v>0.4503763112975233</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-7.573794573545456e-05</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.04979521688201885</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.179850366657236</v>
+        <v>0.4503761314082232</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.0006748763844370842</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.2497952168820189</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.179850408170151</v>
+        <v>0.4503761729211386</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.0007864730432629585</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.4994734148394769</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.179850221362032</v>
+        <v>0.4503759861130193</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.0001962324604392052</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.699473414839477</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.179850290550224</v>
+        <v>0.4503760553012118</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.000860956497490406</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.699473414839477</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.179850089904467</v>
+        <v>0.4503758546554539</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.0004106061533093452</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.699473414839477</v>
+        <v>-0.02000000000000013</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.179850131417382</v>
+        <v>0.4503758961683693</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.001061062328517437</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.699473414839477</v>
+        <v>-0.02000000000000013</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.179850159092659</v>
+        <v>0.4503759238436462</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-Mamba1_repeat_1_000006.xlsx
+++ b/out/Attention-Mamba1_repeat_1_000006.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0.006207163445651531</v>
+        <v>0.006207120604813099</v>
       </c>
       <c r="JB2" t="n">
         <v>0.1199999999999999</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0.006342182867228985</v>
+        <v>0.006342160515487194</v>
       </c>
       <c r="JB3" t="n">
         <v>0.1199999999999999</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0.006411452777683735</v>
+        <v>0.006411434151232243</v>
       </c>
       <c r="JB4" t="n">
         <v>0.7199999999999999</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0.006846233271062374</v>
+        <v>0.006846227683126926</v>
       </c>
       <c r="JB5" t="n">
         <v>0.8599999999999999</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0.005792059935629368</v>
+        <v>0.005792046897113323</v>
       </c>
       <c r="JB6" t="n">
         <v>0.7199999999999999</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0.006360054947435856</v>
+        <v>0.006360066123306751</v>
       </c>
       <c r="JB7" t="n">
         <v>0.7199999999999999</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0.005367246456444263</v>
+        <v>0.005367227829992771</v>
       </c>
       <c r="JB8" t="n">
         <v>0.5799999999999998</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0.006550620310008526</v>
+        <v>0.006550648249685764</v>
       </c>
       <c r="JB9" t="n">
         <v>0.5799999999999998</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0.006490088067948818</v>
+        <v>0.006490063853561878</v>
       </c>
       <c r="JB10" t="n">
         <v>0.4399999999999999</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0.005696640349924564</v>
+        <v>0.005696612410247326</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.16</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0.005532250739634037</v>
+        <v>0.005532241426408291</v>
       </c>
       <c r="JB12" t="n">
         <v>-0.3</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0.00515605416148901</v>
+        <v>0.005156035535037518</v>
       </c>
       <c r="JB13" t="n">
         <v>-0.3</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0.005981327034533024</v>
+        <v>0.005981319583952427</v>
       </c>
       <c r="JB14" t="n">
         <v>-0.4399999999999999</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0.004941192455589771</v>
+        <v>0.00494119618088007</v>
       </c>
       <c r="JB15" t="n">
         <v>-0.5799999999999998</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0.004974578507244587</v>
+        <v>0.004974587820470333</v>
       </c>
       <c r="JB16" t="n">
         <v>-0.7199999999999999</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0.005092139355838299</v>
+        <v>0.005092130042612553</v>
       </c>
       <c r="JB17" t="n">
         <v>-0.7199999999999999</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0.005633248947560787</v>
+        <v>0.005633224733173847</v>
       </c>
       <c r="JB18" t="n">
         <v>-0.5799999999999998</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0.005953357554972172</v>
+        <v>0.005953359417617321</v>
       </c>
       <c r="JB19" t="n">
         <v>-0.5799999999999998</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0.006602124311029911</v>
+        <v>0.006602137349545956</v>
       </c>
       <c r="JB20" t="n">
         <v>-0.5799999999999998</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0.005436302162706852</v>
+        <v>0.005436324514448643</v>
       </c>
       <c r="JB21" t="n">
         <v>-0.5799999999999998</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0.005349772982299328</v>
+        <v>0.00534976739436388</v>
       </c>
       <c r="JB22" t="n">
         <v>-0.7199999999999999</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0.005134754814207554</v>
+        <v>0.005134777165949345</v>
       </c>
       <c r="JB23" t="n">
         <v>-0.8599999999999999</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0.005302916280925274</v>
+        <v>0.005302910692989826</v>
       </c>
       <c r="JB24" t="n">
         <v>-0.8599999999999999</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0.006316087208688259</v>
+        <v>0.006316077895462513</v>
       </c>
       <c r="JB25" t="n">
         <v>-0.5799999999999998</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0.005086249671876431</v>
+        <v>0.005086264573037624</v>
       </c>
       <c r="JB26" t="n">
         <v>0.3</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0.006834325380623341</v>
+        <v>0.00683435145765543</v>
       </c>
       <c r="JB27" t="n">
         <v>0.4399999999999999</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0.009803268127143383</v>
+        <v>0.009803266264498234</v>
       </c>
       <c r="JB28" t="n">
         <v>0.3</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0.005230660550296307</v>
+        <v>0.005230658687651157</v>
       </c>
       <c r="JB30" t="n">
         <v>0.02000000000000007</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0.005556081421673298</v>
+        <v>0.00555607583373785</v>
       </c>
       <c r="JB31" t="n">
         <v>-0.8599999999999999</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0.004580830223858356</v>
+        <v>0.004580850712954998</v>
       </c>
       <c r="JB32" t="n">
         <v>-0.9999999999999998</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0.004326946102082729</v>
+        <v>0.004326905123889446</v>
       </c>
       <c r="JB33" t="n">
         <v>-0.7199999999999999</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0.004814106039702892</v>
+        <v>0.004814081825315952</v>
       </c>
       <c r="JB34" t="n">
         <v>-0.7199999999999999</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0.006981401704251766</v>
+        <v>0.006981396116316319</v>
       </c>
       <c r="JB35" t="n">
         <v>-0.7199999999999999</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0.005062269978225231</v>
+        <v>0.005062281154096127</v>
       </c>
       <c r="JB36" t="n">
         <v>-0.5799999999999998</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0.005026125349104404</v>
+        <v>0.00502608809620142</v>
       </c>
       <c r="JB37" t="n">
         <v>0.02000000000000007</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0.005594893358647823</v>
+        <v>0.005594897083938122</v>
       </c>
       <c r="JB38" t="n">
         <v>-0.2599999999999998</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0.004877683706581593</v>
+        <v>0.004877696745097637</v>
       </c>
       <c r="JB40" t="n">
         <v>0.16</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0.005536851473152637</v>
+        <v>0.005536829121410847</v>
       </c>
       <c r="JB41" t="n">
         <v>0.3</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0.006697596050798893</v>
+        <v>0.006697575561702251</v>
       </c>
       <c r="JB42" t="n">
         <v>0.5799999999999998</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0.006844854913651943</v>
+        <v>0.006844903342425823</v>
       </c>
       <c r="JB43" t="n">
         <v>0.7199999999999999</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0.00935364980250597</v>
+        <v>0.009353651665151119</v>
       </c>
       <c r="JB44" t="n">
         <v>0.5799999999999998</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0.005945404060184956</v>
+        <v>0.005945389159023762</v>
       </c>
       <c r="JB45" t="n">
         <v>0.3</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0.002955780364573002</v>
+        <v>0.002955791540443897</v>
       </c>
       <c r="JB46" t="n">
         <v>0.02000000000000007</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0.005179510451853275</v>
+        <v>0.005179525353014469</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.8599999999999999</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0.004848345182836056</v>
+        <v>0.004848337732255459</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.7199999999999999</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0.003350836224853992</v>
+        <v>0.003350851126015186</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.7199999999999999</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0.006065732799470425</v>
+        <v>0.006065736524760723</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.7199999999999999</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0.004219301976263523</v>
+        <v>0.004219305701553822</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.7199999999999999</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0.004448720254004002</v>
+        <v>0.004448729567229748</v>
       </c>
       <c r="JB52" t="n">
         <v>-0.4399999999999999</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0.003080525435507298</v>
+        <v>0.003080555237829685</v>
       </c>
       <c r="JB53" t="n">
         <v>-0.7199999999999999</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0.007585323415696621</v>
+        <v>0.00758534949272871</v>
       </c>
       <c r="JB54" t="n">
         <v>0.1600000000000001</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0.0009712046012282372</v>
+        <v>0.0009711934253573418</v>
       </c>
       <c r="JB55" t="n">
         <v>0.16</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0.01057935412973166</v>
+        <v>0.01057934109121561</v>
       </c>
       <c r="JB56" t="n">
         <v>0.1600000000000001</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>-0.001564680598676205</v>
+        <v>-0.001564695499837399</v>
       </c>
       <c r="JB57" t="n">
         <v>0.16</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0.0008056936785578728</v>
+        <v>0.0008056787773966789</v>
       </c>
       <c r="JB58" t="n">
         <v>0.4399999999999999</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0.02222119271755219</v>
+        <v>0.02222117036581039</v>
       </c>
       <c r="JB59" t="n">
         <v>0.1600000000000001</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0.008746686391532421</v>
+        <v>0.008746716193854809</v>
       </c>
       <c r="JB60" t="n">
         <v>0.1600000000000001</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>-0.002759278751909733</v>
+        <v>-0.002759271301329136</v>
       </c>
       <c r="JB61" t="n">
         <v>-0.4399999999999999</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>-0.002197650261223316</v>
+        <v>-0.002197633497416973</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.7199999999999999</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>-0.0001791389659047127</v>
+        <v>-0.0001791166141629219</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.9999999999999998</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>-0.0017900625243783</v>
+        <v>-0.001790068112313747</v>
       </c>
       <c r="JB64" t="n">
         <v>-0.9999999999999998</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0.0006416859105229378</v>
+        <v>0.0006416523829102516</v>
       </c>
       <c r="JB65" t="n">
         <v>-0.9999999999999998</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>-0.0007145730778574944</v>
+        <v>-0.000714578665792942</v>
       </c>
       <c r="JB66" t="n">
         <v>-0.9999999999999998</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0.001293000765144825</v>
+        <v>0.001293002627789974</v>
       </c>
       <c r="JB67" t="n">
         <v>-0.9999999999999998</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0.001239358447492123</v>
+        <v>0.001239332370460033</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.9999999999999998</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>9.129848331212997e-05</v>
+        <v>9.131897240877151e-05</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.9999999999999998</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0.001452044583857059</v>
+        <v>0.001452072523534298</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.9999999999999998</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>-0.001405653543770313</v>
+        <v>-0.001405662856996059</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.9999999999999998</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>3.915745764970779e-05</v>
+        <v>3.913883119821548e-05</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.9999999999999998</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0.0001948131248354912</v>
+        <v>0.0001948056742548943</v>
       </c>
       <c r="JB73" t="n">
         <v>-0.9999999999999998</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0.001030710525810719</v>
+        <v>0.001030727289617062</v>
       </c>
       <c r="JB74" t="n">
         <v>-0.9999999999999998</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0.0008104080334305763</v>
+        <v>0.0008103912696242332</v>
       </c>
       <c r="JB75" t="n">
         <v>-0.9999999999999998</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>-0.000362263061106205</v>
+        <v>-0.0003622351214289665</v>
       </c>
       <c r="JB76" t="n">
         <v>-0.9999999999999998</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0.0002335542812943459</v>
+        <v>0.0002335710451006889</v>
       </c>
       <c r="JB77" t="n">
         <v>-0.9999999999999998</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0.0006411010399460793</v>
+        <v>0.0006411382928490639</v>
       </c>
       <c r="JB78" t="n">
         <v>-0.9999999999999998</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>-0.0004367930814623833</v>
+        <v>-0.0004368359223008156</v>
       </c>
       <c r="JB79" t="n">
         <v>-0.9999999999999998</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>-0.0006333636119961739</v>
+        <v>-0.0006333747878670692</v>
       </c>
       <c r="JB81" t="n">
         <v>-0.9999999999999998</v>
@@ -66131,10 +66131,10 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0.001151957549154758</v>
+        <v>0.001151974312961102</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.2599999999999998</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC82" t="n">
         <v>0.4503771484746504</v>
@@ -66926,10 +66926,10 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0.0009500766173005104</v>
+        <v>0.0009500617161393166</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.2599999999999998</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC83" t="n">
         <v>0.4503771692311082</v>
@@ -67721,10 +67721,10 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0.001128560863435268</v>
+        <v>0.001128553412854671</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.2599999999999998</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC84" t="n">
         <v>0.4503772730133966</v>
@@ -68516,10 +68516,10 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>-0.001120119355618954</v>
+        <v>-0.001120130531489849</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.2599999999999998</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC85" t="n">
         <v>0.4503775013344313</v>
@@ -69314,7 +69314,7 @@
         <v>-0.0005965391173958778</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.02000000000000007</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC86" t="n">
         <v>0.4503773767956851</v>
@@ -70106,10 +70106,10 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>-0.0004362137988209724</v>
+        <v>-0.0004361988976597786</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC87" t="n">
         <v>0.450377404470962</v>
@@ -70901,10 +70901,10 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0.001077928580343723</v>
+        <v>0.001077922992408276</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.02000000000000007</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC88" t="n">
         <v>0.4503774598215159</v>
@@ -71696,10 +71696,10 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>-0.001127165742218494</v>
+        <v>-0.001127147115767002</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.02000000000000007</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC89" t="n">
         <v>0.4503777227366467</v>
@@ -72491,10 +72491,10 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>-0.0001120949164032936</v>
+        <v>-0.0001121172681450844</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.02000000000000007</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC90" t="n">
         <v>0.4503776397108158</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>-0.0004843929782509804</v>
+        <v>-0.0004844153299927711</v>
       </c>
       <c r="JB91" t="n">
         <v>-0.2599999999999998</v>
@@ -74084,7 +74084,7 @@
         <v>-0.0005521578714251518</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC92" t="n">
         <v>0.4503774459838774</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>-0.0007966244593262672</v>
+        <v>-0.0007966356351971626</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.9999999999999998</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>-0.0006675319746136665</v>
+        <v>-0.0006675524637103081</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.7199999999999999</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>-0.000567135401070118</v>
+        <v>-0.0005671335384249687</v>
       </c>
       <c r="JB95" t="n">
         <v>-0.7199999999999999</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0.0003354726359248161</v>
+        <v>0.0003355024382472038</v>
       </c>
       <c r="JB96" t="n">
         <v>-0.1199999999999999</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>-0.0008710445836186409</v>
+        <v>-0.0008710408583283424</v>
       </c>
       <c r="JB97" t="n">
         <v>-0.1199999999999999</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>-0.0009327111765742302</v>
+        <v>-0.0009327055886387825</v>
       </c>
       <c r="JB98" t="n">
         <v>-0.1199999999999999</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>-0.0008830046281218529</v>
+        <v>-0.0008830325677990913</v>
       </c>
       <c r="JB99" t="n">
         <v>-0.9999999999999998</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>-0.0005200998857617378</v>
+        <v>-0.0005201036110520363</v>
       </c>
       <c r="JB100" t="n">
         <v>-0.9999999999999998</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>-0.0002966606989502907</v>
+        <v>-0.0002966346219182014</v>
       </c>
       <c r="JB101" t="n">
         <v>-0.7199999999999999</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>-0.0003482317551970482</v>
+        <v>-0.0003482429310679436</v>
       </c>
       <c r="JB102" t="n">
         <v>0.16</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0.0001257872208952904</v>
+        <v>0.0001258095726370811</v>
       </c>
       <c r="JB103" t="n">
         <v>0.1600000000000001</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0.0006639258936047554</v>
+        <v>0.0006639594212174416</v>
       </c>
       <c r="JB104" t="n">
         <v>0.4399999999999999</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>-0.000521278940141201</v>
+        <v>-0.0005212938413023949</v>
       </c>
       <c r="JB105" t="n">
         <v>0.7199999999999999</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0.0002198508009314537</v>
+        <v>0.0002198712900280952</v>
       </c>
       <c r="JB106" t="n">
         <v>0.7199999999999999</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>9.657349437475204e-05</v>
+        <v>9.656045585870743e-05</v>
       </c>
       <c r="JB107" t="n">
         <v>0.5799999999999998</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0.0003365101292729378</v>
+        <v>0.0003364933654665947</v>
       </c>
       <c r="JB108" t="n">
         <v>0.8599999999999999</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0.0003854716196656227</v>
+        <v>0.0003854809328913689</v>
       </c>
       <c r="JB109" t="n">
         <v>0.7199999999999999</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0.0006475178524851799</v>
+        <v>0.0006474936380982399</v>
       </c>
       <c r="JB110" t="n">
         <v>0.5799999999999998</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>-0.0002286871895194054</v>
+        <v>-0.0002286611124873161</v>
       </c>
       <c r="JB111" t="n">
         <v>0.5799999999999998</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0.0003580143675208092</v>
+        <v>0.0003580069169402122</v>
       </c>
       <c r="JB113" t="n">
         <v>-0.16</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0.0003768233582377434</v>
+        <v>0.0003768382593989372</v>
       </c>
       <c r="JB114" t="n">
         <v>-0.02000000000000007</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>-6.425194442272186e-06</v>
+        <v>-6.430782377719879e-06</v>
       </c>
       <c r="JB115" t="n">
         <v>0.1199999999999999</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0.0001192344352602959</v>
+        <v>0.0001192400231957436</v>
       </c>
       <c r="JB116" t="n">
         <v>0.7199999999999999</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>6.986316293478012e-05</v>
+        <v>6.985757499933243e-05</v>
       </c>
       <c r="JB117" t="n">
         <v>0.8599999999999999</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0.001394783146679401</v>
+        <v>0.001394777558743954</v>
       </c>
       <c r="JB118" t="n">
         <v>0.8599999999999999</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0.003585808910429478</v>
+        <v>0.003585833124816418</v>
       </c>
       <c r="JB119" t="n">
         <v>0.8599999999999999</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>-7.573794573545456e-05</v>
+        <v>-7.573608309030533e-05</v>
       </c>
       <c r="JB120" t="n">
         <v>0.8599999999999999</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0.0006748763844370842</v>
+        <v>0.0006748596206307411</v>
       </c>
       <c r="JB121" t="n">
         <v>0.7199999999999999</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0.0007864730432629585</v>
+        <v>0.0007864749059081078</v>
       </c>
       <c r="JB122" t="n">
         <v>-0.02000000000000007</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0.0001962324604392052</v>
+        <v>0.0001962194219231606</v>
       </c>
       <c r="JB123" t="n">
         <v>-0.02000000000000007</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0.000860956497490406</v>
+        <v>0.0008609211072325706</v>
       </c>
       <c r="JB124" t="n">
         <v>-0.02000000000000007</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0.0004106061533093452</v>
+        <v>0.0004105838015675545</v>
       </c>
       <c r="JB125" t="n">
         <v>-0.02000000000000013</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0.001061062328517437</v>
+        <v>0.001061067916452885</v>
       </c>
       <c r="JB126" t="n">
         <v>-0.02000000000000013</v>
